--- a/importusersaspdotnet.xlsx
+++ b/importusersaspdotnet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/55932fd6500e7bf1/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\project\ASP.NET\Furni\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86F2D7CF-CAB1-4564-BA78-4EEBB5D03C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A49125-DDCF-4545-BE23-B7B275B2338A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{C9382EBA-35AB-4D28-A021-5895F0F2C6ED}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C9382EBA-35AB-4D28-A021-5895F0F2C6ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
-  <si>
-    <t>UserName</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>FullName</t>
   </si>
@@ -56,22 +53,28 @@
     <t>Password</t>
   </si>
   <si>
-    <t>quangduy</t>
-  </si>
-  <si>
-    <t>Quang Duy</t>
-  </si>
-  <si>
-    <t>user1@gmail.com</t>
-  </si>
-  <si>
-    <t>thái bình</t>
-  </si>
-  <si>
     <t>Abc123!@#</t>
   </si>
   <si>
-    <t>user2@gmail.com</t>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>USER</t>
+  </si>
+  <si>
+    <t>user4@gmail.com</t>
+  </si>
+  <si>
+    <t>user5@gmail.com</t>
+  </si>
+  <si>
+    <t>hà nội</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nguyễn Văn A</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn B</t>
   </si>
 </sst>
 </file>
@@ -457,15 +460,19 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.77734375" customWidth="1"/>
+    <col min="2" max="2" width="28.44140625" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" customWidth="1"/>
+    <col min="4" max="4" width="24.21875" customWidth="1"/>
+    <col min="6" max="6" width="19.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -477,55 +484,59 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>6</v>
+      <c r="A2" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1234567879</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2">
-        <v>123456789</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>6</v>
+      <c r="A3" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1234567879</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>123456789</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{56F3DE99-7D8E-4212-993E-1F718DCC6D66}"/>
-    <hyperlink ref="F2" r:id="rId2" xr:uid="{229F3081-345C-457C-B520-28B8C5CF255A}"/>
-    <hyperlink ref="C3" r:id="rId3" xr:uid="{65843BA1-D475-471E-914B-36A5B958BC86}"/>
-    <hyperlink ref="F3" r:id="rId4" xr:uid="{94339836-BAC3-4EBB-AE0A-05D6AF40973A}"/>
+    <hyperlink ref="C2" r:id="rId1" display="user1@gmail.com" xr:uid="{56F3DE99-7D8E-4212-993E-1F718DCC6D66}"/>
+    <hyperlink ref="F2" r:id="rId2" display="Abc123!@#" xr:uid="{229F3081-345C-457C-B520-28B8C5CF255A}"/>
+    <hyperlink ref="C3" r:id="rId3" display="user2@gmail.com" xr:uid="{65843BA1-D475-471E-914B-36A5B958BC86}"/>
+    <hyperlink ref="F3" r:id="rId4" display="Abc123!@#" xr:uid="{94339836-BAC3-4EBB-AE0A-05D6AF40973A}"/>
+    <hyperlink ref="A2" r:id="rId5" xr:uid="{F2AE0071-790E-46F3-9D40-A726F543867C}"/>
+    <hyperlink ref="A3" r:id="rId6" xr:uid="{740C990A-E8D3-4730-89F4-C7C3A2DE12E5}"/>
+    <hyperlink ref="E2" r:id="rId7" xr:uid="{566A1887-0684-4E0C-B783-AF4624A18AA7}"/>
+    <hyperlink ref="E3" r:id="rId8" xr:uid="{FF8C3708-4DB5-40B8-999A-A6AF770AD6CC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
